--- a/Result/profitability/2367.xlsx
+++ b/Result/profitability/2367.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.34</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2175</v>
+        <v>0.12125</v>
       </c>
       <c r="N2" t="n">
-        <v>15.0625</v>
+        <v>13.30625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.12</v>
       </c>
       <c r="M3" t="n">
-        <v>0.13625</v>
+        <v>0.03250000000000004</v>
       </c>
       <c r="N3" t="n">
-        <v>14.13375</v>
+        <v>12.75125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.42</v>
       </c>
       <c r="M4" t="n">
-        <v>0.115</v>
+        <v>0.008750000000000042</v>
       </c>
       <c r="N4" t="n">
-        <v>13.6525</v>
+        <v>11.955</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.24</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008750000000000042</v>
+        <v>-0.03124999999999996</v>
       </c>
       <c r="N5" t="n">
-        <v>13.44</v>
+        <v>12.0125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.48</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.06124999999999996</v>
+        <v>-0.09374999999999996</v>
       </c>
       <c r="N6" t="n">
-        <v>11.845</v>
+        <v>11.51</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.07624999999999996</v>
+        <v>-0.1025</v>
       </c>
       <c r="N7" t="n">
-        <v>13.08</v>
+        <v>12.8725</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.24</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.04249999999999995</v>
+        <v>-0.02249999999999995</v>
       </c>
       <c r="N8" t="n">
-        <v>13.54375</v>
+        <v>13.72125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.14</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.08499999999999996</v>
+        <v>-0.08499999999999995</v>
       </c>
       <c r="N11" t="n">
         <v>12.125</v>
@@ -1899,7 +1899,7 @@
         <v>0.3</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.09999999999999996</v>
+        <v>-0.09999999999999995</v>
       </c>
       <c r="N12" t="n">
         <v>12.155</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2367</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4110</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3815</v>
+      </c>
+      <c r="E75" t="n">
+        <v>295</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-220</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-5.35%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>48</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-172</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-167</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.81875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.420000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2461005199306761</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-11.42</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.6136485760343902</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
